--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.25726255777729</v>
+        <v>3.29180516563881</v>
       </c>
       <c r="D2" t="n">
-        <v>20.26616048577696</v>
+        <v>3.293251078938757</v>
       </c>
       <c r="E2" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F2" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.65545813274956</v>
+        <v>3.031511946571804</v>
       </c>
       <c r="D3" t="n">
-        <v>18.76265065619525</v>
+        <v>3.048930731631728</v>
       </c>
       <c r="E3" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F3" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.21782591393008</v>
+        <v>8.160396711013638</v>
       </c>
       <c r="D4" t="n">
-        <v>50.40476615607828</v>
+        <v>8.190774500362721</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F4" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.98123840931075</v>
+        <v>8.446951241512997</v>
       </c>
       <c r="D5" t="n">
-        <v>52.14913364876769</v>
+        <v>8.474234217924751</v>
       </c>
       <c r="E5" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F5" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.67680251641341</v>
+        <v>3.35998040891718</v>
       </c>
       <c r="D6" t="n">
-        <v>20.80371283713067</v>
+        <v>3.380603336033734</v>
       </c>
       <c r="E6" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F6" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.84275841246097</v>
+        <v>5.336948242024907</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81436899225776</v>
+        <v>5.332334961241886</v>
       </c>
       <c r="E7" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F7" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.11895233323954</v>
+        <v>5.869329754151425</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04263488571016</v>
+        <v>5.856928168927902</v>
       </c>
       <c r="E8" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F8" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.83348148620711</v>
+        <v>6.635440741508656</v>
       </c>
       <c r="D9" t="n">
-        <v>40.94041249361209</v>
+        <v>6.652817030211965</v>
       </c>
       <c r="E9" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F9" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.189019521765045</v>
+        <v>0.68071567228682</v>
       </c>
       <c r="D10" t="n">
-        <v>4.026740747447861</v>
+        <v>0.6543453714602775</v>
       </c>
       <c r="E10" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F10" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.06208099435129</v>
+        <v>7.647588161582085</v>
       </c>
       <c r="D11" t="n">
-        <v>47.14125124880233</v>
+        <v>7.660453327930379</v>
       </c>
       <c r="E11" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F11" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.00712408023362</v>
+        <v>7.313657663037964</v>
       </c>
       <c r="D12" t="n">
-        <v>33.60849665547062</v>
+        <v>5.461380706513975</v>
       </c>
       <c r="E12" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F12" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.04608521643319</v>
+        <v>5.207488847670394</v>
       </c>
       <c r="D13" t="n">
-        <v>9.595710729231735</v>
+        <v>1.559302993500157</v>
       </c>
       <c r="E13" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F13" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.33602916168442</v>
+        <v>3.954604738773718</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74468934618036</v>
+        <v>3.046012018754309</v>
       </c>
       <c r="E14" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F14" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.54433537271629</v>
+        <v>4.475954498066397</v>
       </c>
       <c r="D15" t="n">
-        <v>7.415816277778176</v>
+        <v>1.205070145138954</v>
       </c>
       <c r="E15" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F15" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.35077809996145</v>
+        <v>7.532001441243735</v>
       </c>
       <c r="D16" t="n">
-        <v>22.61942355577315</v>
+        <v>3.675656327813136</v>
       </c>
       <c r="E16" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F16" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>43.08064177818402</v>
+        <v>7.000604288954903</v>
       </c>
       <c r="D17" t="n">
-        <v>9.020824987034825</v>
+        <v>1.465884060393159</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F17" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.57081780781622</v>
+        <v>5.780257893770136</v>
       </c>
       <c r="D18" t="n">
-        <v>23.56183787571828</v>
+        <v>3.828798654804221</v>
       </c>
       <c r="E18" t="n">
-        <v>12.8278814102084</v>
+        <v>2.084530729158866</v>
       </c>
       <c r="F18" t="n">
-        <v>14.79371109675199</v>
+        <v>2.403978053222199</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
